--- a/report/models/dev_v1_cleaned_model_comparison.xlsx
+++ b/report/models/dev_v1_cleaned_model_comparison.xlsx
@@ -51,14 +51,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00F8CBAD"/>
+        <bgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
-        <bgColor rgb="00F8CBAD"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -185,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -199,22 +199,23 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -585,8 +586,8 @@
   <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -612,12 +613,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>language</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>mode</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -768,12 +769,12 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
+          <t>no_term</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
           <t>ende</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>no_term</t>
         </is>
       </c>
       <c r="C3" s="5" t="n">
@@ -836,24 +837,20 @@
       <c r="V3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>ende</t>
-        </is>
-      </c>
+      <c r="A4" s="7" t="n"/>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>proper_term</t>
+          <t>enru</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>51.2444459978333</v>
+        <v>28.30072363934785</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>32.31917493311038</v>
+        <v>22.34744080996105</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>36.2882873129007</v>
+        <v>24.89269829150201</v>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
@@ -861,13 +858,13 @@
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>75.69544530598721</v>
+        <v>58.96157104080788</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>64.25464758424178</v>
+        <v>50.71857164156197</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>67.48956991652733</v>
+        <v>52.62708718834202</v>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
@@ -875,149 +872,121 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>80.20833333333334</v>
+        <v/>
       </c>
       <c r="L4" s="5" t="n">
-        <v>72.8125</v>
+        <v/>
       </c>
       <c r="M4" s="5" t="n">
-        <v>72.34375</v>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="N4" s="5" t="n"/>
       <c r="O4" s="5" t="n">
-        <v>0.9788424541467304</v>
+        <v/>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.9774800637958532</v>
+        <v/>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>0.974571620813397</v>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="R4" s="5" t="n"/>
       <c r="S4" s="5" t="n">
-        <v>0.9493087557603689</v>
+        <v/>
       </c>
       <c r="T4" s="5" t="n">
-        <v>0.9447004608294933</v>
+        <v/>
       </c>
       <c r="U4" s="5" t="n">
-        <v>0.9400921658986178</v>
-      </c>
-      <c r="V4" s="6" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
+        <v/>
+      </c>
+      <c r="V4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>ende</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>random_term</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>43.98247955105997</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>27.9951308244768</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>33.35560009041871</v>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>70.2502613196158</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>59.13438319078625</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>62.70730490788958</v>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>82.19438116932423</v>
-      </c>
-      <c r="L5" s="7" t="n">
-        <v>70.23538344722856</v>
-      </c>
-      <c r="M5" s="7" t="n">
-        <v>76.49962034927867</v>
-      </c>
-      <c r="N5" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="O5" s="7" t="n">
-        <v>0.9465645331784954</v>
-      </c>
-      <c r="P5" s="7" t="n">
-        <v>0.9431402325546772</v>
-      </c>
-      <c r="Q5" s="7" t="n">
-        <v>0.9465645331784954</v>
-      </c>
-      <c r="R5" s="9" t="inlineStr">
-        <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="n">
-        <v>0.8803827751196173</v>
-      </c>
-      <c r="T5" s="7" t="n">
-        <v>0.8724082934609246</v>
-      </c>
-      <c r="U5" s="7" t="n">
-        <v>0.8803827751196173</v>
-      </c>
-      <c r="V5" s="9" t="inlineStr">
-        <is>
-          <t>tie</t>
-        </is>
-      </c>
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>enes</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>48.4920980075653</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>38.83409977383212</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>42.1737242292057</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>69.78280913470842</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>63.88473313447336</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>65.85136486380246</v>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="N5" s="8" t="n"/>
+      <c r="O5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="P5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="8" t="n"/>
+      <c r="S5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>enru</t>
+          <t>proper_term</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>no_term</t>
+          <t>ende</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>28.30072363934785</v>
+        <v>51.2444459978333</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>22.34744080996105</v>
+        <v>32.31917493311038</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>24.89269829150201</v>
+        <v>36.2882873129007</v>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
@@ -1025,13 +994,13 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>58.96157104080788</v>
+        <v>75.69544530598721</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>50.71857164156197</v>
+        <v>64.25464758424178</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>52.62708718834202</v>
+        <v>67.48956991652733</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
@@ -1039,45 +1008,53 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v/>
+        <v>80.20833333333334</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v/>
+        <v>72.8125</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n"/>
+        <v>72.34375</v>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
       <c r="O6" s="5" t="n">
-        <v/>
+        <v>0.9788424541467304</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v/>
+        <v>0.9774800637958532</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="5" t="n"/>
+        <v>0.974571620813397</v>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
       <c r="S6" s="5" t="n">
-        <v/>
+        <v>0.9493087557603689</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v/>
+        <v>0.9447004608294933</v>
       </c>
       <c r="U6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="5" t="n"/>
+        <v>0.9400921658986178</v>
+      </c>
+      <c r="V6" s="6" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>enru</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>proper_term</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -1152,106 +1129,102 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>enru</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>random_term</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>32.05830494031198</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>21.84573220142191</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>26.64800305258266</v>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>62.84690263715132</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>51.10134660502143</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>56.40927838653371</v>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>80.95523581135092</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>66.34692246203038</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>75.27977617905674</v>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>0.9306606662721771</v>
-      </c>
-      <c r="P8" s="7" t="n">
-        <v>0.9296978002013974</v>
-      </c>
-      <c r="Q8" s="7" t="n">
-        <v>0.9256646630747351</v>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="n">
-        <v>0.855871886120997</v>
-      </c>
-      <c r="T8" s="7" t="n">
-        <v>0.8576512455516012</v>
-      </c>
-      <c r="U8" s="7" t="n">
-        <v>0.8451957295373673</v>
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>enes</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>61.13116300094295</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>47.58248173916545</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>56.11348123756358</v>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>79.03354646336024</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>69.97206301318633</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>76.02376874031519</v>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>95.75070821529745</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>84.13597733711048</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>92.06798866855524</v>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>0.9724740321057601</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>0.9704640496425198</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>0.9720018885741264</v>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>0.9215686274509802</v>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v>0.9150326797385622</v>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v>0.9215686274509802</v>
       </c>
       <c r="V8" s="12" t="inlineStr">
         <is>
-          <t>Qwen 3B</t>
+          <t>tie</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>enes</t>
+          <t>random_term</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>no_term</t>
+          <t>ende</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>48.4920980075653</v>
+        <v>43.98247955105997</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>38.83409977383212</v>
+        <v>27.9951308244768</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>42.1737242292057</v>
+        <v>33.35560009041871</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -1259,13 +1232,13 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>69.78280913470842</v>
+        <v>70.2502613196158</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>63.88473313447336</v>
+        <v>59.13438319078625</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>65.85136486380246</v>
+        <v>62.70730490788958</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
@@ -1273,55 +1246,63 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v/>
+        <v>82.19438116932423</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v/>
+        <v>70.23538344722856</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n"/>
+        <v>76.49962034927867</v>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
       <c r="O9" s="5" t="n">
-        <v/>
+        <v>0.9465645331784954</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v/>
+        <v>0.9431402325546772</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="5" t="n"/>
+        <v>0.9465645331784954</v>
+      </c>
+      <c r="R9" s="11" t="inlineStr">
+        <is>
+          <t>tie</t>
+        </is>
+      </c>
       <c r="S9" s="5" t="n">
-        <v/>
+        <v>0.8803827751196173</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v/>
+        <v>0.8724082934609246</v>
       </c>
       <c r="U9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="5" t="n"/>
+        <v>0.8803827751196173</v>
+      </c>
+      <c r="V9" s="11" t="inlineStr">
+        <is>
+          <t>tie</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>enes</t>
-        </is>
-      </c>
+      <c r="A10" s="7" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>proper_term</t>
+          <t>enru</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>61.13116300094295</v>
+        <v>32.05830494031198</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>47.58248173916545</v>
+        <v>21.84573220142191</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>56.11348123756358</v>
+        <v>26.64800305258266</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
@@ -1329,13 +1310,13 @@
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>79.03354646336024</v>
+        <v>62.84690263715132</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>69.97206301318633</v>
+        <v>51.10134660502143</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>76.02376874031519</v>
+        <v>56.40927838653371</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
@@ -1343,13 +1324,13 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>95.75070821529745</v>
+        <v>80.95523581135092</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>84.13597733711048</v>
+        <v>66.34692246203038</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>92.06798866855524</v>
+        <v>75.27977617905674</v>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
@@ -1357,13 +1338,13 @@
         </is>
       </c>
       <c r="O10" s="5" t="n">
-        <v>0.9724740321057601</v>
+        <v>0.9306606662721771</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.9704640496425198</v>
+        <v>0.9296978002013974</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>0.9720018885741264</v>
+        <v>0.9256646630747351</v>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
@@ -1371,109 +1352,108 @@
         </is>
       </c>
       <c r="S10" s="5" t="n">
-        <v>0.9215686274509802</v>
+        <v>0.855871886120997</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>0.9150326797385622</v>
+        <v>0.8576512455516012</v>
       </c>
       <c r="U10" s="5" t="n">
-        <v>0.9215686274509802</v>
-      </c>
-      <c r="V10" s="11" t="inlineStr">
-        <is>
-          <t>tie</t>
+        <v>0.8451957295373673</v>
+      </c>
+      <c r="V10" s="13" t="inlineStr">
+        <is>
+          <t>Qwen 3B</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>enes</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>random_term</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="8" t="n">
         <v>50.70684056343824</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="8" t="n">
         <v>40.44581047810417</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="8" t="n">
         <v>44.91161062464971</v>
       </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="n">
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="n">
         <v>72.4054743347176</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="8" t="n">
         <v>65.49073224585894</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="8" t="n">
         <v>68.64749797557563</v>
       </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="n">
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="n">
         <v>96.83544303797468</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="L11" s="8" t="n">
         <v>87.72151898734177</v>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="M11" s="8" t="n">
         <v>93.54430379746836</v>
       </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="O11" s="7" t="n">
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="n">
         <v>0.9597385244853599</v>
       </c>
-      <c r="P11" s="7" t="n">
+      <c r="P11" s="8" t="n">
         <v>0.9561328474619611</v>
       </c>
-      <c r="Q11" s="7" t="n">
+      <c r="Q11" s="8" t="n">
         <v>0.9585570898862037</v>
       </c>
-      <c r="R11" s="8" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="n">
+      <c r="R11" s="9" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="S11" s="8" t="n">
         <v>0.9127272727272731</v>
       </c>
-      <c r="T11" s="7" t="n">
+      <c r="T11" s="8" t="n">
         <v>0.9054545454545456</v>
       </c>
-      <c r="U11" s="7" t="n">
+      <c r="U11" s="8" t="n">
         <v>0.9109090909090911</v>
       </c>
-      <c r="V11" s="8" t="inlineStr">
+      <c r="V11" s="9" t="inlineStr">
         <is>
           <t>GPT</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="10">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A9:A11"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="S1:V1"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A6:A8"/>
     <mergeCell ref="O1:R1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
